--- a/software_developer_forms/002_enhancement_request_form--software_developer_forms.xlsx
+++ b/software_developer_forms/002_enhancement_request_form--software_developer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'type1'}</t>
+          <t>type1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'type1'}</t>
+          <t>type1</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'type2'}</t>
+          <t>type2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'type2'}</t>
+          <t>type2</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'type3'}</t>
+          <t>type3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'type3'}</t>
+          <t>type3</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'new'}</t>
+          <t>new</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'in_progress'}</t>
+          <t>in progress</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'high'}</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'low'}</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'not_assigned'}</t>
+          <t>not_assigned</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'not_assigned'}</t>
+          <t>not assigned</t>
         </is>
       </c>
     </row>
